--- a/public/templates/PBL_Template_วรนาถ.xlsx
+++ b/public/templates/PBL_Template_วรนาถ.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="📝 กรอกคะแนน" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="📤 ATLAS Import" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="📖 คู่มือ" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="📝 กรอกคะแนน" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="📤 ATLAS Import" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="📖 คู่มือ" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -138,7 +138,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -160,11 +160,55 @@
         <color rgb="00BDBDBD"/>
       </bottom>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00BDBDBD"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00BDBDBD"/>
+      </right>
+      <top style="thin">
+        <color rgb="00BDBDBD"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00BDBDBD"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00BDBDBD"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00BDBDBD"/>
+      </right>
+      <top style="thin">
+        <color rgb="00BDBDBD"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00BDBDBD"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="29">
+  <cellXfs count="31">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -250,6 +294,8 @@
     <xf numFmtId="0" fontId="11" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -362,6 +408,28 @@
     </indexedColors>
   </colors>
 </styleSheet>
+</file>
+
+<file path=xl/comments/comment1.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>ATLAS</author>
+  </authors>
+  <commentList>
+    <comment ref="J2" authorId="0" shapeId="0">
+      <text>
+        <t>กรอกปีการศึกษา (พ.ศ.) ของเทอมที่กำลังกรอกจริง เช่น 2569
+⚠️ ตรวจให้ตรงเทอมปัจจุบันทุกครั้ง — กรอกผิดระบบจะไม่ยอมให้นำเข้า</t>
+      </text>
+    </comment>
+    <comment ref="L2" authorId="0" shapeId="0">
+      <text>
+        <t>กรอกภาคเรียน: 1 หรือ 2 (เลือกจาก dropdown)
+⚠️ ตรวจให้ตรงเทอมปัจจุบันทุกครั้ง — กรอกผิดระบบจะไม่ยอมให้นำเข้า</t>
+      </text>
+    </comment>
+  </commentList>
+</comments>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -695,21 +763,13 @@
         </is>
       </c>
       <c r="I2" s="3" t="n"/>
-      <c r="J2" s="4" t="inlineStr">
-        <is>
-          <t>2568</t>
-        </is>
-      </c>
+      <c r="J2" s="4" t="n"/>
       <c r="K2" s="4" t="inlineStr">
         <is>
           <t>เดือน</t>
         </is>
       </c>
-      <c r="L2" s="4" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+      <c r="L2" s="4" t="n"/>
     </row>
     <row r="3" ht="6" customHeight="1"/>
     <row r="4" ht="36" customHeight="1">
@@ -1488,12 +1548,16 @@
       <formula>=$J5="⬜ ผ่าน"</formula>
     </cfRule>
   </conditionalFormatting>
-  <dataValidations count="1">
+  <dataValidations count="2">
     <dataValidation sqref="D5 D6 D7 D8 D9 D10 D11 D12 D13 D14 D15 D16 D17 D18 D19 D20 D21 D22 D23 D24 D25 D26 D27 D28 D29 D30 D31 D32 D33 D34 E5 E6 E7 E8 E9 E10 E11 E12 E13 E14 E15 E16 E17 E18 E19 E20 E21 E22 E23 E24 E25 E26 E27 E28 E29 E30 E31 E32 E33 E34 F5 F6 F7 F8 F9 F10 F11 F12 F13 F14 F15 F16 F17 F18 F19 F20 F21 F22 F23 F24 F25 F26 F27 F28 F29 F30 F31 F32 F33 F34 G5 G6 G7 G8 G9 G10 G11 G12 G13 G14 G15 G16 G17 G18 G19 G20 G21 G22 G23 G24 G25 G26 G27 G28 G29 G30 G31 G32 G33 G34 H5 H6 H7 H8 H9 H10 H11 H12 H13 H14 H15 H16 H17 H18 H19 H20 H21 H22 H23 H24 H25 H26 H27 H28 H29 H30 H31 H32 H33 H34" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="ค่าไม่ถูกต้อง" error="กรุณาเลือก 3 / 2 / 1" type="list">
       <formula1>"3,2,1"</formula1>
     </dataValidation>
+    <dataValidation sqref="L2" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="ภาคเรียนไม่ถูกต้อง" error="ภาคเรียนต้องเป็น 1 หรือ 2 เท่านั้น" promptTitle="ภาคเรียน" prompt="เลือกภาคเรียน 1 หรือ 2 ให้ตรงเทอมปัจจุบัน" type="list">
+      <formula1>"1,2"</formula1>
+    </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
 </worksheet>
 </file>
 
@@ -3727,7 +3791,8 @@
         <is>
           <t>• ชั้น/ห้องต้องพิมพ์รูปแบบ ป.4/KBW (มีเครื่องหมาย /)
 • student_id ต้องตรงกับรหัสในฐานข้อมูล ATLAS
-• ห้ามแก้ไขแท็บ 📤 ATLAS Import โดยตรง</t>
+• ห้ามแก้ไขแท็บ 📤 ATLAS Import โดยตรง
+• ⚠️ ปีการศึกษา (J2) และภาคเรียน (L2) ต้องเป็น "เทอมปัจจุบัน" ที่กำลังกรอกจริง — ตรวจทั้ง 2 ช่องทุกครั้งก่อน Upload (กรอกผิด/เป็นเทอมอนาคต ระบบ ATLAS จะปฏิเสธการนำเข้า)</t>
         </is>
       </c>
     </row>
@@ -3818,6 +3883,8 @@
           <t>💡  สรุป: ครูกรอกจริงเพียง 1 ครั้งต่อโปรเจกต์ (สัปดาห์ 4)  |  30 คน × 5 ด้าน = 150 ช่อง dropdown  |  ~15–20 นาที</t>
         </is>
       </c>
+      <c r="B16" s="29" t="n"/>
+      <c r="C16" s="30" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="3">
